--- a/plantillas/50.xlsx
+++ b/plantillas/50.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$3</definedName>
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/50.xlsx
+++ b/plantillas/50.xlsx
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/50.xlsx
+++ b/plantillas/50.xlsx
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
